--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -1,130 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="31">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>FOTO_INCIDENCIA</t>
-  </si>
-  <si>
-    <t>CASTAÑO</t>
-  </si>
-  <si>
-    <t>GALLETERA ITALIA, C.A.</t>
-  </si>
-  <si>
-    <t>MUSACEUM, C.A.</t>
-  </si>
-  <si>
-    <t>4225</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>2026-05-05</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>NEYDI JAZPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FERNANDO CABRERA </t>
-  </si>
-  <si>
-    <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
-  </si>
-  <si>
-    <t>TIPO A</t>
-  </si>
-  <si>
-    <t>NRO DE FACTURA ERRADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRO DE FACTURA ERRONEO </t>
-  </si>
-  <si>
-    <t>SIN_FOTO</t>
-  </si>
-  <si>
-    <t>NINGUNA</t>
-  </si>
-  <si>
-    <t>HIST_20260504170125</t>
-  </si>
-  <si>
-    <t>ID_20260505101640</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -143,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -437,134 +407,339 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GALLETERA ITALIA, C.A.</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>10685</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>NEYDI JAZPE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HIST_20260504170125</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>10685</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C.P.A. BEJUMA, C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>73689</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO CABRERA </t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" t="s">
-        <v>28</v>
-      </c>
-      <c r="M2" t="s">
-        <v>29</v>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260505140646</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MUSACEUM, C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4225</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO CABRERA </t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NRO DE FACTURA ERRADO_x000D_
+</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>30</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260505101640</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EL TUNAL, C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>119930</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO CABRERA </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260506092700</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,7 +50,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -412,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +550,7 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -612,6 +614,7 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -676,6 +679,7 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -688,10 +692,8 @@
           <t>EL TUNAL, C.A.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>119930</t>
-        </is>
+      <c r="C5" t="n">
+        <v>119930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -741,8 +743,75 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DICOSTRA, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>19873</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO CABRERA </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO SE RECIBIERON 4UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>26752.jpeg.jpeg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260506140600</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +557,6 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,7 +620,6 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,7 +684,6 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -743,7 +747,6 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -791,7 +794,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="1" t="n">
         <v>17.96</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -809,7 +812,6 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +550,7 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -620,6 +614,7 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,6 +679,7 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -747,6 +743,7 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -759,10 +756,8 @@
           <t>DICOSTRA, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>19873</t>
-        </is>
+      <c r="C6" t="n">
+        <v>19873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -794,7 +789,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" t="n">
         <v>17.96</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -812,6 +807,69 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NEYDI JAZPE</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ERROR AL CARGAR EL NRO DE FACTURA </t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260507140540</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,6 +870,72 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IMPROSA, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19104</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NEYDI JAZPE</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU NO PERTENECE A LA RECEPCIÓN.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE CARGO 1 SKU DE MAS QUE NO PERTENECE A LA RECEPCION </t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260507141945</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -882,10 +882,8 @@
           <t>IMPROSA, C.A.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>19104</t>
-        </is>
+      <c r="C8" t="n">
+        <v>19104</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -936,6 +934,136 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA BBQ, C.A.</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>176</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ROBER GIL </t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NRO DE CPNTROL ERRADO </t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ID_20260511092913</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>FABRICA DE HIELO EL OSO, C.A.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>40853</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MARCOS GARCIA </t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FALTA SELLO, FIRMA O CÉDULA.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>FALTO EL SELLO DE LA SUCURSAL</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>ID_20260511132922</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +557,6 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,7 +620,6 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,7 +684,6 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -743,7 +747,6 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -789,7 +792,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="1" t="n">
         <v>17.96</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -807,7 +810,6 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -820,7 +822,6 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -869,7 +870,6 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -933,7 +933,6 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -997,7 +996,6 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1063,7 +1061,6 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1008,10 +1008,8 @@
           <t>FABRICA DE HIELO EL OSO, C.A.</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>40853</t>
-        </is>
+      <c r="C10" t="n">
+        <v>40853</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1059,6 +1057,323 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>ID_20260511132922</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH, C.A.</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>25304</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO CABRERA </t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE DUPLICO EL SKU DE MENTA Y FALTO EL SKU DE ARANDANOS </t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>ID_20260512092016</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH, C.A.</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>25304</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FERNANDO CABRERA </t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE DUPLICO EL SKU DE MENTA Y FALTO EL SKU DE ARANDANOS </t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>ID_20260512092020</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ALGARCA 68GC, C.A.</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1072</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>BARBARA ROMERO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>DOCUMENTO NO LEGIBLE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO SE VISUALIZA LA CANTIDAD EN LA NOTA AL DORSO POR QUE LA FOTO SALIO RECORTADA </t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>ID_20260512114009</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ALGARCA 68GC, C.A.</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1072</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>BARBARA ROMERO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>ID_20260512122053</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DISTRIBUIDORA PARADIS FRESH, C.A.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>33229</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DEVOLUCION</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NEYDI JAZPE </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SE DUPLICO EL SKU DEL AJI DULCE</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>ID_20260512132340</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,6 +550,7 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -620,6 +614,7 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -684,6 +679,7 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -747,6 +743,7 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -792,7 +789,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" t="n">
         <v>17.96</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -810,6 +807,7 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -822,6 +820,7 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -870,6 +869,7 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -933,6 +933,7 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -996,6 +997,7 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1059,6 +1061,7 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1122,6 +1125,7 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1185,6 +1189,7 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1248,6 +1253,7 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1311,6 +1317,7 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1323,10 +1330,8 @@
           <t>DISTRIBUIDORA PARADIS FRESH, C.A.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>33229</t>
-        </is>
+      <c r="C15" t="n">
+        <v>33229</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1376,6 +1381,73 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>I.T.C. DISTRIBUCIONES, C.A.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>U48320</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>NEYDI JAZPE</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>PRODUCTO O SKU DUPLICADO.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE DUPLICO EL SKU DEL CAFE DELLA NONNA 200 GR </t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>ID_20260512161021</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,12 +26,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -550,7 +557,6 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -614,7 +620,6 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -679,7 +684,6 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -743,7 +747,6 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -789,7 +792,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="1" t="n">
         <v>17.96</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -807,7 +810,6 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -820,7 +822,6 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -869,7 +870,6 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -933,7 +933,6 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -997,7 +996,6 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1061,7 +1059,6 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1125,7 +1122,6 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1189,7 +1185,6 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1253,7 +1248,6 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1317,7 +1311,6 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1381,7 +1374,6 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1447,7 +1439,6 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QUESERA Y CHARCUTERIA CAMILA, C.A.</t>
+          <t>ALIMENTOS POLAR COMERCIAL, C.A.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>31272</t>
+          <t>7242101258</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1558,25 +1558,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARCOS GARCIA </t>
+          <t>NEYDI JAZPE</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EL LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALÑTANTE DE 100 GR </t>
-        </is>
-      </c>
-      <c r="J18" s="1" t="n">
+          <t>NRO DE FACTURA ERRADO</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>ID_20260514131312</t>
+          <t>ID_20260514133558</t>
         </is>
       </c>
     </row>
@@ -1603,12 +1603,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ALIMENTOS POLAR COMERCIAL, C.A.</t>
+          <t>QUESERA Y CHARCUTERIA CAMILA, C.A.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>7242101258</t>
+          <t>31272</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1623,40 +1623,40 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>NEYDI JAZPE</t>
+          <t xml:space="preserve">MARCOS GARCIA </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>NRO DE FACTURA ERRADO</t>
-        </is>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
+          <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALÑTANTE DE 100 GR </t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>2.83</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>COB_152620_0.jpeg</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ID_20260514133558</t>
+          <t>ID_20260514131312</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -37,6 +37,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
         <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
   </fills>
@@ -52,9 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2701,6 +2708,76 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA  LATIN FRUITS, C.A.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>006847</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YORBIN ZORRILLA </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>NO SE INDICÓ DIFERENCIA AL DORSO DE LA FACTURA.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>ID_20260602095105</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>INC_095105_0.webp</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,6 +552,7 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,6 +618,7 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -697,6 +685,7 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -762,6 +751,7 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -774,6 +764,7 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -822,6 +813,7 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -887,6 +879,7 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -952,6 +945,7 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1017,6 +1011,7 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1082,6 +1077,7 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1147,6 +1143,7 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1212,6 +1209,7 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1277,6 +1275,7 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1342,6 +1341,7 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1407,6 +1407,7 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1472,6 +1473,7 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1537,6 +1539,7 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1602,6 +1605,7 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1649,7 +1653,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1667,6 +1671,7 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1732,6 +1737,7 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1779,7 +1785,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1797,6 +1803,7 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1862,6 +1869,7 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1927,6 +1935,7 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1992,6 +2001,7 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2057,6 +2067,7 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2122,6 +2133,7 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2187,6 +2199,7 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2252,6 +2265,7 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2317,6 +2331,7 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2382,6 +2397,7 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2447,6 +2463,7 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2512,6 +2529,7 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2577,6 +2595,7 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2642,6 +2661,7 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2707,6 +2727,7 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2754,7 +2775,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2772,11 +2793,7 @@
           <t>ID_20260602095105</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>INC_095105_0.webp</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +566,6 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -618,7 +631,6 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -685,7 +697,6 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -751,7 +762,6 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -764,7 +774,6 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -813,7 +822,6 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,7 +887,6 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -945,7 +952,6 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1011,7 +1017,6 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1077,7 +1082,6 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1143,7 +1147,6 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1209,7 +1212,6 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1275,7 +1277,6 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1341,7 +1342,6 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1407,7 +1407,6 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1473,7 +1472,6 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1539,7 +1537,6 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1605,7 +1602,6 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1653,7 +1649,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="1" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1671,7 +1667,6 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1737,7 +1732,6 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1785,7 +1779,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="1" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1803,7 +1797,6 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1869,7 +1862,6 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1935,7 +1927,6 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2001,7 +1992,6 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2067,7 +2057,6 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2133,7 +2122,6 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2199,7 +2187,6 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2265,7 +2252,6 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2331,7 +2317,6 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2397,7 +2382,6 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2463,7 +2447,6 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2529,7 +2512,6 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2595,7 +2577,6 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2661,7 +2642,6 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2727,7 +2707,6 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2775,7 +2754,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="2" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2793,7 +2772,11 @@
           <t>ID_20260602095105</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>INC_095105_0.webp INC_095146_0.webp INC_095146_1.jpeg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,10 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,6 +552,7 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,6 +618,7 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -697,6 +685,7 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -762,6 +751,7 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -774,6 +764,7 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -822,6 +813,7 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -887,6 +879,7 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -952,6 +945,7 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1017,6 +1011,7 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1082,6 +1077,7 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1147,6 +1143,7 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1212,6 +1209,7 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1277,6 +1275,7 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1342,6 +1341,7 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1407,6 +1407,7 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1472,6 +1473,7 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1537,6 +1539,7 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1602,6 +1605,7 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1649,7 +1653,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1667,6 +1671,7 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1732,6 +1737,7 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1779,7 +1785,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1797,6 +1803,7 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1862,6 +1869,7 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1927,6 +1935,7 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1992,6 +2001,7 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2057,6 +2067,7 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2122,6 +2133,7 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2187,6 +2199,7 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2252,6 +2265,7 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2317,6 +2331,7 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2382,6 +2397,7 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2447,6 +2463,7 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2512,6 +2529,7 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2577,6 +2595,7 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2642,6 +2661,7 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2707,6 +2727,7 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2754,7 +2775,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2774,7 +2795,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>INC_095105_0.webp INC_095146_0.webp INC_095146_1.jpeg</t>
+          <t>INC_095146_0.webp INC_095146_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,12 +26,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -552,7 +573,6 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -618,7 +638,6 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -685,7 +704,6 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -751,7 +769,6 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -764,7 +781,6 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -813,7 +829,6 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,7 +894,6 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -945,7 +959,6 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1011,7 +1024,6 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1077,7 +1089,6 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1143,7 +1154,6 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1209,7 +1219,6 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1275,7 +1284,6 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1341,7 +1349,6 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1407,7 +1414,6 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1473,7 +1479,6 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1539,7 +1544,6 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1605,7 +1609,6 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1653,7 +1656,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="1" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1671,7 +1674,6 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1737,7 +1739,6 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1785,7 +1786,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="1" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1803,7 +1804,6 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1869,7 +1869,6 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1935,7 +1934,6 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2001,7 +1999,6 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2067,7 +2064,6 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2133,7 +2129,6 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2199,7 +2194,6 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2265,7 +2259,6 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2331,7 +2324,6 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2397,7 +2389,6 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2463,7 +2454,6 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2529,7 +2519,6 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2595,7 +2584,6 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2661,7 +2649,6 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2727,7 +2714,6 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2775,7 +2761,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="2" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2796,6 +2782,76 @@
       <c r="N36" t="inlineStr">
         <is>
           <t>INC_095146_0.webp INC_095146_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA  LATIN FRUITS, C.A.</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>006847</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YORBIN ZORRILLA </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>OTRAS.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN LA NOTA AL DORSO COLOCARON 18.8 KG LO QUE GENERO UN EXCEDENTE DE 130.4 KG </t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>369.03</v>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>EXCEDENTES</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>ID_20260602105823</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>INC_105823_0.webp INC_105823_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2821,11 +2821,6 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN LA NOTA AL DORSO COLOCARON 18.8 KG LO QUE GENERO UN EXCEDENTE DE 130.4 KG </t>
@@ -2852,6 +2847,76 @@
       <c r="N37" t="inlineStr">
         <is>
           <t>INC_105823_0.webp INC_105823_1.jpeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>CASTAÑO</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>AGROPECUARIA  LATIN FRUITS, C.A.</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>006847</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">YORBIN ZORRILLA </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN EL APLICATIVO EA COLOCARON 142.2 KG LO QUE GENERO UN FALTANTE DE 7 KG </t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>ID_20260602110929</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>INC_110929_0.webp INC_110929_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,30 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,6 +552,7 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -638,6 +618,7 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -704,6 +685,7 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,6 +751,7 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -781,6 +764,7 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -829,6 +813,7 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -894,6 +879,7 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -959,6 +945,7 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1024,6 +1011,7 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1089,6 +1077,7 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1154,6 +1143,7 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1219,6 +1209,7 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1284,6 +1275,7 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1349,6 +1341,7 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1414,6 +1407,7 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1479,6 +1473,7 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1544,6 +1539,7 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1609,6 +1605,7 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1656,7 +1653,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1674,6 +1671,7 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1739,6 +1737,7 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1786,7 +1785,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1804,6 +1803,7 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1869,6 +1869,7 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1934,6 +1935,7 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1999,6 +2001,7 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2064,6 +2067,7 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2129,6 +2133,7 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2194,6 +2199,7 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2259,6 +2265,7 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2324,6 +2331,7 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2389,6 +2397,7 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2454,6 +2463,7 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2519,6 +2529,7 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2584,6 +2595,7 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2649,6 +2661,7 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2714,6 +2727,7 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2761,7 +2775,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2821,12 +2835,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN LA NOTA AL DORSO COLOCARON 18.8 KG LO QUE GENERO UN EXCEDENTE DE 130.4 KG </t>
         </is>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="J37" t="n">
         <v>369.03</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -2896,7 +2911,7 @@
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN EL APLICATIVO EA COLOCARON 142.2 KG LO QUE GENERO UN FALTANTE DE 7 KG </t>
         </is>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J38" t="n">
         <v>19.81</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -2916,7 +2931,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>INC_110929_0.webp INC_110929_1.jpeg</t>
+          <t>INC_110929_1.jpeg</t>
         </is>
       </c>
     </row>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -2929,11 +2929,7 @@
           <t>ID_20260602110929</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>INC_110929_1.jpeg</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,12 +26,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +573,6 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -618,7 +638,6 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -685,7 +704,6 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -751,7 +769,6 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -764,7 +781,6 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -813,7 +829,6 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,7 +894,6 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -945,7 +959,6 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1011,7 +1024,6 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1077,7 +1089,6 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1143,7 +1154,6 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1209,7 +1219,6 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1275,7 +1284,6 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1341,7 +1349,6 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1407,7 +1414,6 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1473,7 +1479,6 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1539,7 +1544,6 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1605,7 +1609,6 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1653,7 +1656,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="1" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1671,7 +1674,6 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1737,7 +1739,6 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1785,7 +1786,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="1" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1803,7 +1804,6 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1869,7 +1869,6 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1935,7 +1934,6 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2001,7 +1999,6 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2067,7 +2064,6 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2133,7 +2129,6 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2199,7 +2194,6 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2265,7 +2259,6 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2331,7 +2324,6 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2397,7 +2389,6 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2463,7 +2454,6 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2529,7 +2519,6 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2595,7 +2584,6 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2661,7 +2649,6 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2727,7 +2714,6 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2775,7 +2761,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="2" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2835,13 +2821,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN LA NOTA AL DORSO COLOCARON 18.8 KG LO QUE GENERO UN EXCEDENTE DE 130.4 KG </t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="3" t="n">
         <v>369.03</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -2911,7 +2896,7 @@
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN EL APLICATIVO EA COLOCARON 142.2 KG LO QUE GENERO UN FALTANTE DE 7 KG </t>
         </is>
       </c>
-      <c r="J38" t="n">
+      <c r="J38" s="2" t="n">
         <v>19.81</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -2929,7 +2914,11 @@
           <t>ID_20260602110929</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>INC_111358_0.png</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,30 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor rgb="FF00B0F0"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,6 +552,7 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -638,6 +618,7 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -704,6 +685,7 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,6 +751,7 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -781,6 +764,7 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -829,6 +813,7 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -894,6 +879,7 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -959,6 +945,7 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1024,6 +1011,7 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1089,6 +1077,7 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1154,6 +1143,7 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1219,6 +1209,7 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1284,6 +1275,7 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1349,6 +1341,7 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1414,6 +1407,7 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1479,6 +1473,7 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1544,6 +1539,7 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1609,6 +1605,7 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1656,7 +1653,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1674,6 +1671,7 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1739,6 +1737,7 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1786,7 +1785,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1804,6 +1803,7 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1869,6 +1869,7 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1934,6 +1935,7 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1999,6 +2001,7 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2064,6 +2067,7 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2129,6 +2133,7 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2194,6 +2199,7 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2259,6 +2265,7 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2324,6 +2331,7 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2389,6 +2397,7 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2454,6 +2463,7 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2519,6 +2529,7 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2584,6 +2595,7 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2649,6 +2661,7 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2714,6 +2727,7 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2761,7 +2775,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" s="2" t="n">
+      <c r="J36" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2821,12 +2835,13 @@
           <t>OTRAS.</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN LA NOTA AL DORSO COLOCARON 18.8 KG LO QUE GENERO UN EXCEDENTE DE 130.4 KG </t>
         </is>
       </c>
-      <c r="J37" s="3" t="n">
+      <c r="J37" t="n">
         <v>369.03</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -2896,7 +2911,7 @@
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN EL APLICATIVO EA COLOCARON 142.2 KG LO QUE GENERO UN FALTANTE DE 7 KG </t>
         </is>
       </c>
-      <c r="J38" s="2" t="n">
+      <c r="J38" t="n">
         <v>19.81</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -2914,11 +2929,7 @@
           <t>ID_20260602110929</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>INC_111358_0.png</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/CASTAÑO.xlsx
+++ b/cuadros/MAYO/CASTAÑO.xlsx
@@ -26,12 +26,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor rgb="FF00B0F0"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +64,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -552,7 +573,6 @@
           <t>HIST_20260504170125</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -618,7 +638,6 @@
           <t>ID_20260505140646</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -685,7 +704,6 @@
           <t>ID_20260505101640</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -751,7 +769,6 @@
           <t>ID_20260506092700</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -764,7 +781,6 @@
           <t>PEPSI-COLA DE VENEZUELA, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>2026-05-07</t>
@@ -813,7 +829,6 @@
           <t>ID_20260507140540</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,7 +894,6 @@
           <t>ID_20260507141945</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -945,7 +959,6 @@
           <t>ID_20260511132922</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1011,7 +1024,6 @@
           <t>ID_20260512092016</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1077,7 +1089,6 @@
           <t>ID_20260512092020</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1143,7 +1154,6 @@
           <t>ID_20260512114009</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1209,7 +1219,6 @@
           <t>ID_20260512122053</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1275,7 +1284,6 @@
           <t>ID_20260512132340</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1341,7 +1349,6 @@
           <t>ID_20260512161021</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1407,7 +1414,6 @@
           <t>ID_20260514113317</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1473,7 +1479,6 @@
           <t>ID_20260514133558</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1539,7 +1544,6 @@
           <t>ID_20260518083109</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1605,7 +1609,6 @@
           <t>ID_20260518154927</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1653,7 +1656,7 @@
           <t xml:space="preserve">NO SE RECIBIERON 4 UNDS DE YOGURT LIQUIDO FRESA 400 ML Y NO SE COLOCO NOTA AL DORSO DE LA FACTURA </t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="J19" s="1" t="n">
         <v>17.96</v>
       </c>
       <c r="K19" t="inlineStr">
@@ -1671,7 +1674,6 @@
           <t>ID_20260506140600</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1737,7 +1739,6 @@
           <t>ID_20260511092913</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1785,7 +1786,7 @@
           <t xml:space="preserve">SE RECIBIERON 5.4 KG DE QUESO AMARILLO EDAMS CAMILA  Y EN LA NOTA AL DORSO SE COLOCARON 5.5 KG LO QUE GENERO UN FALTANTE DE 100 GR </t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="J21" s="1" t="n">
         <v>2.83</v>
       </c>
       <c r="K21" t="inlineStr">
@@ -1803,7 +1804,6 @@
           <t>ID_20260514131312</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1869,7 +1869,6 @@
           <t>ID_20260519131247</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1935,7 +1934,6 @@
           <t>ID_20260519151546</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2001,7 +1999,6 @@
           <t>ID_20260521152016</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2067,7 +2064,6 @@
           <t>ID_20260526101734</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2133,7 +2129,6 @@
           <t>ID_20260526103631</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2199,7 +2194,6 @@
           <t>ID_20260526103734</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2265,7 +2259,6 @@
           <t>ID_20260527133225</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2331,7 +2324,6 @@
           <t>ID_20260527160915</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2397,7 +2389,6 @@
           <t>ID_20260528101845</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2463,7 +2454,6 @@
           <t>ID_20260528131250</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2529,7 +2519,6 @@
           <t>ID_20260528132418</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2595,7 +2584,6 @@
           <t>ID_20260528160329</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2661,7 +2649,6 @@
           <t>ID_20260601081839</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2727,7 +2714,6 @@
           <t>ID_20260601083230</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2775,7 +2761,7 @@
           <t>NO SE COLOCO LA NOTA AL DORSO DEL OCUMO CHINO LO CUAL GENERO UN FALTANTE DE 6.2 KG , AL RELIAZAR LA CORRECCION DE LA NOTA SE OBTIENE UN RECUPERATIVO DE 8.06 $</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="J36" s="2" t="n">
         <v>8.06</v>
       </c>
       <c r="K36" t="inlineStr">
@@ -2835,13 +2821,12 @@
           <t>OTRAS.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN LA NOTA AL DORSO COLOCARON 18.8 KG LO QUE GENERO UN EXCEDENTE DE 130.4 KG </t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="J37" s="3" t="n">
         <v>369.03</v>
       </c>
       <c r="K37" t="inlineStr">
@@ -2908,10 +2893,10 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN EL APLICATIVO EA COLOCARON 142.2 KG LO QUE GENERO UN FALTANTE DE 7 KG </t>
-        </is>
-      </c>
-      <c r="J38" t="n">
+          <t xml:space="preserve">SE RECIBIERON 149.2 KG DE LIMON Y EN EL APLICATIVO EVA COLOCARON 142.2 KG LO QUE GENERO UN FALTANTE DE 7 KG </t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
         <v>19.81</v>
       </c>
       <c r="K38" t="inlineStr">
@@ -2929,7 +2914,11 @@
           <t>ID_20260602110929</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>INC_111552_0.jpeg INC_111552_1.jpeg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
